--- a/lesson_11/task_04.xlsx
+++ b/lesson_11/task_04.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Перший аркуш" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,63 +413,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ім'я</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Клас</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Вік</t>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Number</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Євген</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" t="n">
-        <v>10</v>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Иван</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2350099597</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Сашко</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>12</v>
+          <t>654321</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Алена</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0013242219</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Михайло</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C4" t="n">
-        <v>18</v>
+          <t>111222</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1297513100</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>222333</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8790472437</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>333444</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8039411877</t>
+        </is>
       </c>
     </row>
   </sheetData>
